--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.73456268593135</v>
+        <v>3.856866436463845</v>
       </c>
       <c r="D2" t="n">
-        <v>2.96214028468669</v>
+        <v>0.4813477962615871</v>
       </c>
       <c r="E2" t="n">
-        <v>15.07399298414345</v>
+        <v>2.44952385992331</v>
       </c>
       <c r="F2" t="n">
-        <v>7.573000586170665</v>
+        <v>1.230612595252733</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.32920788189605</v>
+        <v>6.228496280808109</v>
       </c>
       <c r="D3" t="n">
-        <v>22.20371273939482</v>
+        <v>3.608103320151658</v>
       </c>
       <c r="E3" t="n">
-        <v>15.07399298414345</v>
+        <v>2.44952385992331</v>
       </c>
       <c r="F3" t="n">
-        <v>7.573000586170665</v>
+        <v>1.230612595252733</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.10901151546964</v>
+        <v>7.492714371263816</v>
       </c>
       <c r="D4" t="n">
-        <v>4.924428900898052</v>
+        <v>0.8002196963959335</v>
       </c>
       <c r="E4" t="n">
-        <v>15.07399298414345</v>
+        <v>2.44952385992331</v>
       </c>
       <c r="F4" t="n">
-        <v>7.573000586170665</v>
+        <v>1.230612595252733</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.51610119695297</v>
+        <v>10.64636644450486</v>
       </c>
       <c r="D5" t="n">
-        <v>7.401894978361629</v>
+        <v>1.202807933983765</v>
       </c>
       <c r="E5" t="n">
-        <v>15.07399298414345</v>
+        <v>2.44952385992331</v>
       </c>
       <c r="F5" t="n">
-        <v>7.573000586170665</v>
+        <v>1.230612595252733</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
